--- a/Risultati/Excel/RAW vs EMBEDDING.xlsx
+++ b/Risultati/Excel/RAW vs EMBEDDING.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gassi\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gassi\OneDrive\Desktop\Risultati\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E5BBED6-DBBD-4A9B-B21C-79E7154308D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0792A8BC-97A3-47F7-8F2B-EB26DA6A2533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{72B8679B-EEFC-4B6A-AC1E-FEA3AA10D3E7}"/>
   </bookViews>
@@ -86,9 +86,6 @@
     <t>Confusion Matrix [[TN, FP], [FN, TP]]</t>
   </si>
   <si>
-    <t>RAW</t>
-  </si>
-  <si>
     <t>0.7858</t>
   </si>
   <si>
@@ -182,9 +179,6 @@
     <t>all-MiniLM-L6-v2</t>
   </si>
   <si>
-    <t>SEMANTIC</t>
-  </si>
-  <si>
     <t>0.7959</t>
   </si>
   <si>
@@ -291,6 +285,12 @@
   </si>
   <si>
     <t>[[12540, 954], [5307, 8234]]</t>
+  </si>
+  <si>
+    <t>ORIGINAL</t>
+  </si>
+  <si>
+    <t>EMBEDDING</t>
   </si>
 </sst>
 </file>
@@ -738,43 +738,43 @@
         <v>3</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D2" s="2">
+        <v>2381</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="2">
-        <v>2381</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="O2" s="2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.3">
@@ -782,43 +782,43 @@
         <v>5</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="D3" s="2">
         <v>2381</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I3" s="2" t="s">
+      <c r="K3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.3">
@@ -826,43 +826,43 @@
         <v>7</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2">
         <v>2381</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J4" s="2" t="s">
+      <c r="K4" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N4" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O4" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N4" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O4" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.3">
@@ -870,607 +870,607 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="D5" s="2">
         <v>2381</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N5" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2">
         <v>3</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D7" s="2">
+        <v>2381</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J7" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D7" s="2">
-        <v>2381</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="K7" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J7" s="2" t="s">
+      <c r="L7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>49</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2">
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D8" s="2">
+        <v>2381</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D8" s="2">
-        <v>2381</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="K8" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L8" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N8" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O8" s="2" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2">
         <v>7</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D9" s="2">
         <v>2381</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>55</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="M9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2">
         <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D10" s="2">
         <v>2381</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L10" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B12" s="2">
         <v>3</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D12" s="2">
+        <v>2381</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J12" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="2">
-        <v>2381</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>49</v>
-      </c>
       <c r="K12" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B13" s="2">
         <v>5</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D13" s="2">
         <v>2381</v>
       </c>
       <c r="E13" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" s="2" t="s">
         <v>63</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="N13" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B14" s="2">
         <v>7</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D14" s="2">
         <v>2381</v>
       </c>
       <c r="E14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="2" t="s">
+      <c r="N14" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="O14" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="K14" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B15" s="2">
         <v>9</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D15" s="2">
         <v>2381</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2">
         <v>3</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D17" s="2">
         <v>2381</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O17" s="2" t="s">
         <v>73</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L17" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B18" s="2">
         <v>5</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D18" s="2">
         <v>2381</v>
       </c>
       <c r="E18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O18" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="K18" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L18" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M18" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B19" s="2">
         <v>7</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D19" s="2">
         <v>2381</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="K19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="M19" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="N19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="O19" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="K19" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="L19" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="M19" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="O19" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B20" s="2">
         <v>9</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>47</v>
+        <v>83</v>
       </c>
       <c r="D20" s="2">
         <v>2381</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>
